--- a/results/breakdown/2050/nitrous oxide production, AON 100, green ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 100, green ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.1372585875926995</v>
+        <v>0.2104521880568682</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.1395824622037438</v>
+        <v>0.209760151976082</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0003602590578176867</v>
+        <v>0.0003975910233074946</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-0.002556973159987019</v>
+        <v>0.0002804890212159799</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>-0.0001271577008650675</v>
+        <v>1.394865570718024E-05</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/results/breakdown/2050/nitrous oxide production, AON 100, green ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 100, green ammonia.xlsx
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.209760151976082</v>
+        <v>0.2097601519760821</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0003975910233074946</v>
+        <v>0.000397591023307495</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.0002804890212159799</v>
+        <v>0.0002804890212159755</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>1.394865570718024E-05</v>
+        <v>1.394865570717995E-05</v>
       </c>
       <c r="E6">
         <v>1</v>
